--- a/artfynd/A 47429-2021 artfynd.xlsx
+++ b/artfynd/A 47429-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47429-2021 artfynd.xlsx
+++ b/artfynd/A 47429-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102913746</v>
+        <v>102913748</v>
       </c>
       <c r="B2" t="n">
-        <v>100188</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -759,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -787,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102913748</v>
+        <v>102913746</v>
       </c>
       <c r="B3" t="n">
-        <v>103528</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -871,6 +860,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,7 +877,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 47429-2021 artfynd.xlsx
+++ b/artfynd/A 47429-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102913748</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,8 +895,17 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102913746</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>